--- a/data/trans_dic/IP16A06-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes</t>
+          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,88</t>
+          <t>0,0; 13,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 20,97</t>
+          <t>2,52; 21,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,25</t>
+          <t>0,0; 17,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,19</t>
+          <t>0,0; 20,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,71</t>
+          <t>0,0; 13,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,12</t>
+          <t>1,4; 12,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 13,13</t>
+          <t>1,36; 12,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,0</t>
+          <t>0,0; 9,89</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 6,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 3,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,64</t>
+          <t>0,63; 5,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 4,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,41</t>
+          <t>0,77; 4,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,43</t>
+          <t>0,27; 2,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,26; 2,47</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,23</t>
+          <t>0,0; 9,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 7,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,03</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,53</t>
+          <t>0,48; 4,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,88</t>
+          <t>0,43; 4,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,88</t>
+          <t>0,82; 4,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,56</t>
+          <t>0,37; 3,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,73</t>
+          <t>0,4; 3,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,78</t>
+          <t>0,84; 3,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,01</t>
+          <t>0,7; 2,88</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,07</t>
+          <t>0,36; 2,03</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3032</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>643; 5605</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3315</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4195</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3154</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>592; 5229</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>660; 6123</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3129</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1871</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3316</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2156</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1738</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5039</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4562</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2876</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>553; 5075</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4090</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4118</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1295; 7402</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>648; 6055</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>528; 5027</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4432</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2769</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3089</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3699</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2043</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2947</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5256</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5614</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>600; 5792</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>801; 7718</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3906</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1181; 6741</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>717; 7266</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>592; 5602</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2267; 9719</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2647; 10913</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1113; 6298</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A06-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Estudios-trans_dic.xlsx
@@ -678,27 +678,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,75</t>
+          <t>0,0; 16,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 21,96</t>
+          <t>2,56; 21,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,58</t>
+          <t>0,0; 20,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,71</t>
+          <t>0,0; 20,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,8</t>
+          <t>0,0; 16,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,36</t>
+          <t>1,41; 12,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,66</t>
+          <t>1,37; 12,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,89</t>
+          <t>0,0; 9,74</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,24</t>
+          <t>0,0; 6,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,95</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,0; 2,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,79</t>
+          <t>0,63; 5,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,22</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,4</t>
+          <t>0,71; 4,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,53</t>
+          <t>0,27; 2,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,47</t>
+          <t>0,26; 2,25</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,8</t>
+          <t>0,0; 8,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,35</t>
+          <t>0,0; 8,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,62</t>
+          <t>0,48; 4,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,13</t>
+          <t>0,44; 4,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,71</t>
+          <t>0,83; 4,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,79</t>
+          <t>0,36; 3,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,78</t>
+          <t>0,39; 3,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,62</t>
+          <t>0,96; 3,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,88</t>
+          <t>0,69; 2,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,03</t>
+          <t>0,36; 2,11</t>
         </is>
       </c>
     </row>
@@ -1306,27 +1306,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3032</t>
+          <t>0; 3634</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>643; 5605</t>
+          <t>653; 5465</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3315</t>
+          <t>0; 3800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4195</t>
+          <t>0; 4117</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3154</t>
+          <t>0; 3668</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>592; 5229</t>
+          <t>596; 5182</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>660; 6123</t>
+          <t>665; 6141</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3129</t>
+          <t>0; 3082</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5039</t>
+          <t>0; 5108</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4562</t>
+          <t>0; 4114</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2876</t>
+          <t>0; 2660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>553; 5075</t>
+          <t>555; 4924</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4090</t>
+          <t>0; 4611</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4118</t>
+          <t>0; 4308</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1295; 7402</t>
+          <t>1194; 7374</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>648; 6055</t>
+          <t>644; 5865</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>528; 5027</t>
+          <t>523; 4587</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4432</t>
+          <t>0; 3779</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2769</t>
+          <t>0; 3305</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3089</t>
+          <t>0; 3574</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3699</t>
+          <t>0; 3301</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>600; 5792</t>
+          <t>597; 5896</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>801; 7718</t>
+          <t>816; 7603</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3906</t>
+          <t>0; 4043</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1181; 6741</t>
+          <t>1193; 6906</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>717; 7266</t>
+          <t>691; 6602</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>592; 5602</t>
+          <t>584; 5067</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2267; 9719</t>
+          <t>2568; 10459</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2647; 10913</t>
+          <t>2626; 11063</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1113; 6298</t>
+          <t>1107; 6564</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A06-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A06-Estudios-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6,63%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,71%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,34%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3,27%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,48</t>
+          <t>0,0; 20,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 21,41</t>
+          <t>0,0; 12,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,32</t>
+          <t>0,0; 13,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,05</t>
+          <t>2,56; 20,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 17,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,25</t>
+          <t>1,4; 12,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 12,7</t>
+          <t>1,39; 13,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,74</t>
+          <t>0,0; 10,0</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,33</t>
+          <t>0,63; 5,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,51</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,62</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,74</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,41</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 4,38</t>
+          <t>0,72; 4,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,45</t>
+          <t>0,27; 2,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,25</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
     </row>
@@ -850,27 +850,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -903,29 +903,29 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,23</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 8,67</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,35</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,78</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 4,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,7</t>
+          <t>0,87; 4,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,07</t>
+          <t>0,36; 3,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,4; 3,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,82</t>
+          <t>0,48; 4,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,45</t>
+          <t>0,43; 3,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,42</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,9</t>
+          <t>0,92; 3,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,92</t>
+          <t>0,7; 3,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,11</t>
+          <t>0,34; 2,07</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1099,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron  tranquilizantes, relajantes (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2129</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1343</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3634</t>
+          <t>0; 4089</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>653; 5465</t>
+          <t>0; 2904</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3800</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4117</t>
+          <t>0; 3059</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3668</t>
+          <t>653; 5353</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3252</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>596; 5182</t>
+          <t>593; 5127</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>665; 6141</t>
+          <t>675; 6352</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3082</t>
+          <t>0; 3164</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1871</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1214</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1445</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>818</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>524</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1871</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1214</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5108</t>
+          <t>553; 4943</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4114</t>
+          <t>0; 4800</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2660</t>
+          <t>0; 3827</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>555; 4924</t>
+          <t>0; 4812</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4611</t>
+          <t>0; 4353</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4308</t>
+          <t>0; 2665</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1194; 7374</t>
+          <t>1213; 7425</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>644; 5865</t>
+          <t>649; 5805</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>523; 4587</t>
+          <t>0; 4610</t>
         </is>
       </c>
     </row>
@@ -1531,27 +1531,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1584,27 +1584,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1637,29 +1637,29 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0; 3724</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3266</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3779</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3305</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3574</t>
+          <t>0; 3668</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3301</t>
+          <t>0; 2903</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3213</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2043</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2947</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1141</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3213</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2667</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>597; 5896</t>
+          <t>1249; 6991</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>816; 7603</t>
+          <t>689; 6824</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4043</t>
+          <t>589; 5531</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1193; 6906</t>
+          <t>596; 5677</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>691; 6602</t>
+          <t>798; 7263</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>584; 5067</t>
+          <t>0; 3951</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2568; 10459</t>
+          <t>2468; 10157</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2626; 11063</t>
+          <t>2631; 11380</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1107; 6564</t>
+          <t>1048; 6442</t>
         </is>
       </c>
     </row>
